--- a/artfynd/A 23439-2024 artfynd.xlsx
+++ b/artfynd/A 23439-2024 artfynd.xlsx
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117894257</v>
+        <v>117894275</v>
       </c>
       <c r="B8" t="n">
-        <v>57287</v>
+        <v>90517</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,21 +1333,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>448356</v>
+        <v>448679</v>
       </c>
       <c r="R8" t="n">
-        <v>7094667</v>
+        <v>7094568</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,11 +1393,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117894275</v>
+        <v>117894257</v>
       </c>
       <c r="B9" t="n">
-        <v>90517</v>
+        <v>57287</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1440,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>448679</v>
+        <v>448356</v>
       </c>
       <c r="R9" t="n">
-        <v>7094568</v>
+        <v>7094667</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,6 +1495,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,7 +1526,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117894259</v>
+        <v>117894245</v>
       </c>
       <c r="B10" t="n">
         <v>57287</v>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>448513</v>
+        <v>448717</v>
       </c>
       <c r="R10" t="n">
-        <v>7094687</v>
+        <v>7094543</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1740,7 +1740,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117894245</v>
+        <v>117894259</v>
       </c>
       <c r="B12" t="n">
         <v>57287</v>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>448717</v>
+        <v>448513</v>
       </c>
       <c r="R12" t="n">
-        <v>7094543</v>
+        <v>7094687</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2703,10 +2703,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117894262</v>
+        <v>117894271</v>
       </c>
       <c r="B21" t="n">
-        <v>57287</v>
+        <v>57398</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2715,20 +2715,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2736,17 +2736,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rörvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>448775</v>
+        <v>448815</v>
       </c>
       <c r="R21" t="n">
-        <v>7094632</v>
+        <v>7094592</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2779,11 +2795,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2810,10 +2821,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117894271</v>
+        <v>117894262</v>
       </c>
       <c r="B22" t="n">
-        <v>57398</v>
+        <v>57287</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2822,20 +2833,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2843,33 +2854,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Rörvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>448815</v>
+        <v>448775</v>
       </c>
       <c r="R22" t="n">
-        <v>7094592</v>
+        <v>7094632</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2902,6 +2897,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3244,10 +3244,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117894272</v>
+        <v>117894249</v>
       </c>
       <c r="B26" t="n">
-        <v>90517</v>
+        <v>57287</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3260,21 +3260,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3284,10 +3284,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>448832</v>
+        <v>448332</v>
       </c>
       <c r="R26" t="n">
-        <v>7094454</v>
+        <v>7094545</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3320,6 +3320,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3346,10 +3351,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117894249</v>
+        <v>117894272</v>
       </c>
       <c r="B27" t="n">
-        <v>57287</v>
+        <v>90517</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3362,21 +3367,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3386,10 +3391,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>448332</v>
+        <v>448832</v>
       </c>
       <c r="R27" t="n">
-        <v>7094545</v>
+        <v>7094454</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3422,11 +3427,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 23439-2024 artfynd.xlsx
+++ b/artfynd/A 23439-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117894250</v>
+        <v>117894256</v>
       </c>
       <c r="B2" t="n">
         <v>57287</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>448221</v>
+        <v>448339</v>
       </c>
       <c r="R2" t="n">
-        <v>7094520</v>
+        <v>7094675</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117894265</v>
+        <v>117894246</v>
       </c>
       <c r="B3" t="n">
         <v>57287</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>448787</v>
+        <v>448706</v>
       </c>
       <c r="R3" t="n">
-        <v>7094595</v>
+        <v>7094549</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117894252</v>
+        <v>117894276</v>
       </c>
       <c r="B4" t="n">
-        <v>57287</v>
+        <v>90517</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>448177</v>
+        <v>448261</v>
       </c>
       <c r="R4" t="n">
-        <v>7094570</v>
+        <v>7094615</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117894266</v>
+        <v>117894267</v>
       </c>
       <c r="B5" t="n">
         <v>57287</v>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>448814</v>
+        <v>448851</v>
       </c>
       <c r="R5" t="n">
-        <v>7094591</v>
+        <v>7094596</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117894263</v>
+        <v>117894252</v>
       </c>
       <c r="B6" t="n">
         <v>57287</v>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>448782</v>
+        <v>448177</v>
       </c>
       <c r="R6" t="n">
-        <v>7094627</v>
+        <v>7094570</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117894248</v>
+        <v>117894275</v>
       </c>
       <c r="B7" t="n">
-        <v>57287</v>
+        <v>90517</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>448541</v>
+        <v>448679</v>
       </c>
       <c r="R7" t="n">
-        <v>7094570</v>
+        <v>7094568</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,11 +1281,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117894275</v>
+        <v>117894270</v>
       </c>
       <c r="B8" t="n">
-        <v>90517</v>
+        <v>57287</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>448679</v>
+        <v>448883</v>
       </c>
       <c r="R8" t="n">
-        <v>7094568</v>
+        <v>7094577</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,6 +1383,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,7 +1414,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117894257</v>
+        <v>117894247</v>
       </c>
       <c r="B9" t="n">
         <v>57287</v>
@@ -1459,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>448356</v>
+        <v>448551</v>
       </c>
       <c r="R9" t="n">
-        <v>7094667</v>
+        <v>7094566</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1526,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117894245</v>
+        <v>117894271</v>
       </c>
       <c r="B10" t="n">
-        <v>57287</v>
+        <v>57398</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1538,20 +1533,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1559,17 +1554,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rörvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>448717</v>
+        <v>448815</v>
       </c>
       <c r="R10" t="n">
-        <v>7094543</v>
+        <v>7094592</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,11 +1613,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,7 +1639,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117894256</v>
+        <v>117894262</v>
       </c>
       <c r="B11" t="n">
         <v>57287</v>
@@ -1673,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>448339</v>
+        <v>448775</v>
       </c>
       <c r="R11" t="n">
-        <v>7094675</v>
+        <v>7094632</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,7 +1719,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1847,7 +1853,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117894247</v>
+        <v>117894257</v>
       </c>
       <c r="B13" t="n">
         <v>57287</v>
@@ -1887,10 +1893,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>448551</v>
+        <v>448356</v>
       </c>
       <c r="R13" t="n">
-        <v>7094566</v>
+        <v>7094667</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2061,7 +2067,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117894270</v>
+        <v>117894254</v>
       </c>
       <c r="B15" t="n">
         <v>57287</v>
@@ -2101,10 +2107,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>448883</v>
+        <v>448299</v>
       </c>
       <c r="R15" t="n">
-        <v>7094577</v>
+        <v>7094650</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2168,7 +2174,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117894251</v>
+        <v>117894245</v>
       </c>
       <c r="B16" t="n">
         <v>57287</v>
@@ -2208,10 +2214,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>448162</v>
+        <v>448717</v>
       </c>
       <c r="R16" t="n">
-        <v>7094481</v>
+        <v>7094543</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2275,7 +2281,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117894258</v>
+        <v>117894268</v>
       </c>
       <c r="B17" t="n">
         <v>57287</v>
@@ -2315,10 +2321,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>448394</v>
+        <v>448849</v>
       </c>
       <c r="R17" t="n">
-        <v>7094732</v>
+        <v>7094603</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2355,7 +2361,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2382,7 +2388,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117894254</v>
+        <v>117894258</v>
       </c>
       <c r="B18" t="n">
         <v>57287</v>
@@ -2422,10 +2428,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>448299</v>
+        <v>448394</v>
       </c>
       <c r="R18" t="n">
-        <v>7094650</v>
+        <v>7094732</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2462,7 +2468,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2489,7 +2495,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117894267</v>
+        <v>117894249</v>
       </c>
       <c r="B19" t="n">
         <v>57287</v>
@@ -2529,10 +2535,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>448851</v>
+        <v>448332</v>
       </c>
       <c r="R19" t="n">
-        <v>7094596</v>
+        <v>7094545</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2569,7 +2575,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2596,7 +2602,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117894269</v>
+        <v>117894266</v>
       </c>
       <c r="B20" t="n">
         <v>57287</v>
@@ -2636,10 +2642,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>448847</v>
+        <v>448814</v>
       </c>
       <c r="R20" t="n">
-        <v>7094604</v>
+        <v>7094591</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2703,10 +2709,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117894271</v>
+        <v>117894251</v>
       </c>
       <c r="B21" t="n">
-        <v>57398</v>
+        <v>57287</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2715,20 +2721,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2736,33 +2742,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rörvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>448815</v>
+        <v>448162</v>
       </c>
       <c r="R21" t="n">
-        <v>7094592</v>
+        <v>7094481</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2795,6 +2785,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2821,7 +2816,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117894262</v>
+        <v>117894264</v>
       </c>
       <c r="B22" t="n">
         <v>57287</v>
@@ -2861,10 +2856,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>448775</v>
+        <v>448772</v>
       </c>
       <c r="R22" t="n">
-        <v>7094632</v>
+        <v>7094608</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2928,7 +2923,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117894255</v>
+        <v>117894253</v>
       </c>
       <c r="B23" t="n">
         <v>57287</v>
@@ -2968,10 +2963,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>448322</v>
+        <v>448220</v>
       </c>
       <c r="R23" t="n">
-        <v>7094686</v>
+        <v>7094592</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3008,7 +3003,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3035,7 +3030,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117894268</v>
+        <v>117894265</v>
       </c>
       <c r="B24" t="n">
         <v>57287</v>
@@ -3075,10 +3070,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>448849</v>
+        <v>448787</v>
       </c>
       <c r="R24" t="n">
-        <v>7094603</v>
+        <v>7094595</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3115,7 +3110,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3142,7 +3137,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117894276</v>
+        <v>117894272</v>
       </c>
       <c r="B25" t="n">
         <v>90517</v>
@@ -3182,10 +3177,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>448261</v>
+        <v>448832</v>
       </c>
       <c r="R25" t="n">
-        <v>7094615</v>
+        <v>7094454</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3244,7 +3239,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117894249</v>
+        <v>117894255</v>
       </c>
       <c r="B26" t="n">
         <v>57287</v>
@@ -3284,10 +3279,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>448332</v>
+        <v>448322</v>
       </c>
       <c r="R26" t="n">
-        <v>7094545</v>
+        <v>7094686</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3351,10 +3346,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117894272</v>
+        <v>117894263</v>
       </c>
       <c r="B27" t="n">
-        <v>90517</v>
+        <v>57287</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3367,21 +3362,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3391,10 +3386,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>448832</v>
+        <v>448782</v>
       </c>
       <c r="R27" t="n">
-        <v>7094454</v>
+        <v>7094627</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3427,6 +3422,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3555,7 +3555,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117894246</v>
+        <v>117894248</v>
       </c>
       <c r="B29" t="n">
         <v>57287</v>
@@ -3595,10 +3595,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>448706</v>
+        <v>448541</v>
       </c>
       <c r="R29" t="n">
-        <v>7094549</v>
+        <v>7094570</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3635,7 +3635,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3662,7 +3662,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117894264</v>
+        <v>117894269</v>
       </c>
       <c r="B30" t="n">
         <v>57287</v>
@@ -3702,10 +3702,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>448772</v>
+        <v>448847</v>
       </c>
       <c r="R30" t="n">
-        <v>7094608</v>
+        <v>7094604</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3742,7 +3742,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3769,7 +3769,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117894253</v>
+        <v>117894250</v>
       </c>
       <c r="B31" t="n">
         <v>57287</v>
@@ -3809,10 +3809,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>448220</v>
+        <v>448221</v>
       </c>
       <c r="R31" t="n">
-        <v>7094592</v>
+        <v>7094520</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 23439-2024 artfynd.xlsx
+++ b/artfynd/A 23439-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117894256</v>
+        <v>117894259</v>
       </c>
       <c r="B2" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>448339</v>
+        <v>448513</v>
       </c>
       <c r="R2" t="n">
-        <v>7094675</v>
+        <v>7094687</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117894246</v>
+        <v>117894250</v>
       </c>
       <c r="B3" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>448706</v>
+        <v>448221</v>
       </c>
       <c r="R3" t="n">
-        <v>7094549</v>
+        <v>7094520</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117894276</v>
+        <v>117894257</v>
       </c>
       <c r="B4" t="n">
-        <v>90517</v>
+        <v>57288</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>448261</v>
+        <v>448356</v>
       </c>
       <c r="R4" t="n">
-        <v>7094615</v>
+        <v>7094667</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117894267</v>
+        <v>117894247</v>
       </c>
       <c r="B5" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>448851</v>
+        <v>448551</v>
       </c>
       <c r="R5" t="n">
-        <v>7094596</v>
+        <v>7094566</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117894252</v>
+        <v>117894267</v>
       </c>
       <c r="B6" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>448177</v>
+        <v>448851</v>
       </c>
       <c r="R6" t="n">
-        <v>7094570</v>
+        <v>7094596</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117894275</v>
+        <v>117894258</v>
       </c>
       <c r="B7" t="n">
-        <v>90517</v>
+        <v>57288</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>448679</v>
+        <v>448394</v>
       </c>
       <c r="R7" t="n">
-        <v>7094568</v>
+        <v>7094732</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,6 +1286,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117894270</v>
+        <v>117894254</v>
       </c>
       <c r="B8" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>448883</v>
+        <v>448299</v>
       </c>
       <c r="R8" t="n">
-        <v>7094577</v>
+        <v>7094650</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117894247</v>
+        <v>117894246</v>
       </c>
       <c r="B9" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>448551</v>
+        <v>448706</v>
       </c>
       <c r="R9" t="n">
-        <v>7094566</v>
+        <v>7094549</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117894271</v>
+        <v>117894265</v>
       </c>
       <c r="B10" t="n">
-        <v>57398</v>
+        <v>57288</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1533,20 +1543,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1554,33 +1564,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rörvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>448815</v>
+        <v>448787</v>
       </c>
       <c r="R10" t="n">
-        <v>7094592</v>
+        <v>7094595</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1613,6 +1607,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1639,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117894262</v>
+        <v>117894260</v>
       </c>
       <c r="B11" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1679,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>448775</v>
+        <v>448747</v>
       </c>
       <c r="R11" t="n">
-        <v>7094632</v>
+        <v>7094597</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1746,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117894259</v>
+        <v>117894270</v>
       </c>
       <c r="B12" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1786,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>448513</v>
+        <v>448883</v>
       </c>
       <c r="R12" t="n">
-        <v>7094687</v>
+        <v>7094577</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1826,7 +1825,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1853,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117894257</v>
+        <v>117894252</v>
       </c>
       <c r="B13" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1893,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>448356</v>
+        <v>448177</v>
       </c>
       <c r="R13" t="n">
-        <v>7094667</v>
+        <v>7094570</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1960,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117894260</v>
+        <v>117894272</v>
       </c>
       <c r="B14" t="n">
-        <v>57287</v>
+        <v>90519</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1976,21 +1975,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2000,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>448747</v>
+        <v>448832</v>
       </c>
       <c r="R14" t="n">
-        <v>7094597</v>
+        <v>7094454</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2036,11 +2035,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2067,10 +2061,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117894254</v>
+        <v>117894271</v>
       </c>
       <c r="B15" t="n">
-        <v>57287</v>
+        <v>57399</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2079,20 +2073,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2100,17 +2094,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rörvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>448299</v>
+        <v>448815</v>
       </c>
       <c r="R15" t="n">
-        <v>7094650</v>
+        <v>7094592</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2143,11 +2153,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2174,10 +2179,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117894245</v>
+        <v>117894249</v>
       </c>
       <c r="B16" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2214,10 +2219,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>448717</v>
+        <v>448332</v>
       </c>
       <c r="R16" t="n">
-        <v>7094543</v>
+        <v>7094545</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2254,7 +2259,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2281,10 +2286,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117894268</v>
+        <v>117894269</v>
       </c>
       <c r="B17" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2321,10 +2326,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>448849</v>
+        <v>448847</v>
       </c>
       <c r="R17" t="n">
-        <v>7094603</v>
+        <v>7094604</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2361,7 +2366,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2388,10 +2393,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117894258</v>
+        <v>117894253</v>
       </c>
       <c r="B18" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2428,10 +2433,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>448394</v>
+        <v>448220</v>
       </c>
       <c r="R18" t="n">
-        <v>7094732</v>
+        <v>7094592</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2468,7 +2473,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2495,10 +2500,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117894249</v>
+        <v>117894264</v>
       </c>
       <c r="B19" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2535,10 +2540,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>448332</v>
+        <v>448772</v>
       </c>
       <c r="R19" t="n">
-        <v>7094545</v>
+        <v>7094608</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2575,7 +2580,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2602,10 +2607,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117894266</v>
+        <v>117894245</v>
       </c>
       <c r="B20" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2642,10 +2647,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>448814</v>
+        <v>448717</v>
       </c>
       <c r="R20" t="n">
-        <v>7094591</v>
+        <v>7094543</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2682,7 +2687,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2709,10 +2714,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117894251</v>
+        <v>117894274</v>
       </c>
       <c r="B21" t="n">
-        <v>57287</v>
+        <v>90519</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2725,21 +2730,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2749,10 +2754,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>448162</v>
+        <v>448764</v>
       </c>
       <c r="R21" t="n">
-        <v>7094481</v>
+        <v>7094544</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2785,11 +2790,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2816,10 +2816,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117894264</v>
+        <v>117894276</v>
       </c>
       <c r="B22" t="n">
-        <v>57287</v>
+        <v>90519</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2832,21 +2832,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2856,10 +2856,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>448772</v>
+        <v>448261</v>
       </c>
       <c r="R22" t="n">
-        <v>7094608</v>
+        <v>7094615</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2892,11 +2892,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2923,10 +2918,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117894253</v>
+        <v>117894266</v>
       </c>
       <c r="B23" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2963,10 +2958,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>448220</v>
+        <v>448814</v>
       </c>
       <c r="R23" t="n">
-        <v>7094592</v>
+        <v>7094591</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3003,7 +2998,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3030,10 +3025,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117894265</v>
+        <v>117894263</v>
       </c>
       <c r="B24" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3070,10 +3065,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>448787</v>
+        <v>448782</v>
       </c>
       <c r="R24" t="n">
-        <v>7094595</v>
+        <v>7094627</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3110,7 +3105,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3137,10 +3132,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117894272</v>
+        <v>117894256</v>
       </c>
       <c r="B25" t="n">
-        <v>90517</v>
+        <v>57288</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3153,21 +3148,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3177,10 +3172,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>448832</v>
+        <v>448339</v>
       </c>
       <c r="R25" t="n">
-        <v>7094454</v>
+        <v>7094675</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3213,6 +3208,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3239,10 +3239,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117894255</v>
+        <v>117894251</v>
       </c>
       <c r="B26" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3279,10 +3279,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>448322</v>
+        <v>448162</v>
       </c>
       <c r="R26" t="n">
-        <v>7094686</v>
+        <v>7094481</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3346,10 +3346,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117894263</v>
+        <v>117894255</v>
       </c>
       <c r="B27" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3386,10 +3386,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>448782</v>
+        <v>448322</v>
       </c>
       <c r="R27" t="n">
-        <v>7094627</v>
+        <v>7094686</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3453,10 +3453,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117894274</v>
+        <v>117894262</v>
       </c>
       <c r="B28" t="n">
-        <v>90517</v>
+        <v>57288</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3469,21 +3469,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>448764</v>
+        <v>448775</v>
       </c>
       <c r="R28" t="n">
-        <v>7094544</v>
+        <v>7094632</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3529,6 +3529,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3558,7 +3563,7 @@
         <v>117894248</v>
       </c>
       <c r="B29" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3662,10 +3667,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117894269</v>
+        <v>117894268</v>
       </c>
       <c r="B30" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3702,10 +3707,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>448847</v>
+        <v>448849</v>
       </c>
       <c r="R30" t="n">
-        <v>7094604</v>
+        <v>7094603</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3742,7 +3747,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3769,10 +3774,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117894250</v>
+        <v>117894275</v>
       </c>
       <c r="B31" t="n">
-        <v>57287</v>
+        <v>90519</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3785,21 +3790,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3809,10 +3814,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>448221</v>
+        <v>448679</v>
       </c>
       <c r="R31" t="n">
-        <v>7094520</v>
+        <v>7094568</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3845,11 +3850,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 23439-2024 artfynd.xlsx
+++ b/artfynd/A 23439-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117894266</v>
+        <v>117894245</v>
       </c>
       <c r="B2" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>448814</v>
+        <v>448717</v>
       </c>
       <c r="R2" t="n">
-        <v>7094591</v>
+        <v>7094543</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117894263</v>
+        <v>117894246</v>
       </c>
       <c r="B3" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>448782</v>
+        <v>448706</v>
       </c>
       <c r="R3" t="n">
-        <v>7094627</v>
+        <v>7094549</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117894254</v>
+        <v>117894247</v>
       </c>
       <c r="B4" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>448299</v>
+        <v>448551</v>
       </c>
       <c r="R4" t="n">
-        <v>7094650</v>
+        <v>7094566</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +954,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,15 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117894274</v>
+        <v>117894248</v>
       </c>
       <c r="B5" t="n">
-        <v>90521</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,21 +992,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>448764</v>
+        <v>448541</v>
       </c>
       <c r="R5" t="n">
-        <v>7094544</v>
+        <v>7094570</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,6 +1052,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,15 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117894269</v>
+        <v>117894249</v>
       </c>
       <c r="B6" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>448847</v>
+        <v>448332</v>
       </c>
       <c r="R6" t="n">
-        <v>7094604</v>
+        <v>7094545</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,15 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117894265</v>
+        <v>117894250</v>
       </c>
       <c r="B7" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1245,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>448787</v>
+        <v>448221</v>
       </c>
       <c r="R7" t="n">
-        <v>7094595</v>
+        <v>7094520</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1260,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,15 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117894260</v>
+        <v>117894251</v>
       </c>
       <c r="B8" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1352,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>448747</v>
+        <v>448162</v>
       </c>
       <c r="R8" t="n">
-        <v>7094597</v>
+        <v>7094481</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,15 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117894268</v>
+        <v>117894252</v>
       </c>
       <c r="B9" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>448849</v>
+        <v>448177</v>
       </c>
       <c r="R9" t="n">
-        <v>7094603</v>
+        <v>7094570</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1526,15 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117894259</v>
+        <v>117894253</v>
       </c>
       <c r="B10" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>448513</v>
+        <v>448220</v>
       </c>
       <c r="R10" t="n">
-        <v>7094687</v>
+        <v>7094592</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1633,15 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117894258</v>
+        <v>117894254</v>
       </c>
       <c r="B11" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1673,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>448394</v>
+        <v>448299</v>
       </c>
       <c r="R11" t="n">
-        <v>7094732</v>
+        <v>7094650</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,7 +1668,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1740,15 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117894270</v>
+        <v>117894255</v>
       </c>
       <c r="B12" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1780,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>448883</v>
+        <v>448322</v>
       </c>
       <c r="R12" t="n">
-        <v>7094577</v>
+        <v>7094686</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1847,15 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117894275</v>
+        <v>117894256</v>
       </c>
       <c r="B13" t="n">
-        <v>90521</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1808,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1832,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>448679</v>
+        <v>448339</v>
       </c>
       <c r="R13" t="n">
-        <v>7094568</v>
+        <v>7094675</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1923,6 +1868,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,15 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117894272</v>
+        <v>117894257</v>
       </c>
       <c r="B14" t="n">
-        <v>90521</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1965,21 +1910,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1989,10 +1934,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>448832</v>
+        <v>448356</v>
       </c>
       <c r="R14" t="n">
-        <v>7094454</v>
+        <v>7094667</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2025,6 +1970,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2051,15 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117894245</v>
+        <v>117894258</v>
       </c>
       <c r="B15" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2091,10 +2036,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>448717</v>
+        <v>448394</v>
       </c>
       <c r="R15" t="n">
-        <v>7094543</v>
+        <v>7094732</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2131,7 +2076,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2158,15 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117894253</v>
+        <v>117894259</v>
       </c>
       <c r="B16" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2198,10 +2138,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>448220</v>
+        <v>448513</v>
       </c>
       <c r="R16" t="n">
-        <v>7094592</v>
+        <v>7094687</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,15 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117894250</v>
+        <v>117894260</v>
       </c>
       <c r="B17" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2305,10 +2240,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>448221</v>
+        <v>448747</v>
       </c>
       <c r="R17" t="n">
-        <v>7094520</v>
+        <v>7094597</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2372,32 +2307,27 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117894271</v>
+        <v>117894262</v>
       </c>
       <c r="B18" t="n">
-        <v>57401</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2405,33 +2335,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rörvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>448815</v>
+        <v>448775</v>
       </c>
       <c r="R18" t="n">
-        <v>7094592</v>
+        <v>7094632</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2464,6 +2378,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2490,15 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117894267</v>
+        <v>117894263</v>
       </c>
       <c r="B19" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2530,10 +2444,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>448851</v>
+        <v>448782</v>
       </c>
       <c r="R19" t="n">
-        <v>7094596</v>
+        <v>7094627</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2597,15 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117894248</v>
+        <v>117894264</v>
       </c>
       <c r="B20" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2637,10 +2546,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>448541</v>
+        <v>448772</v>
       </c>
       <c r="R20" t="n">
-        <v>7094570</v>
+        <v>7094608</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2677,7 +2586,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2704,15 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117894247</v>
+        <v>117894265</v>
       </c>
       <c r="B21" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2744,10 +2648,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>448551</v>
+        <v>448787</v>
       </c>
       <c r="R21" t="n">
-        <v>7094566</v>
+        <v>7094595</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2784,7 +2688,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2811,15 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117894246</v>
+        <v>117894266</v>
       </c>
       <c r="B22" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2851,10 +2750,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>448706</v>
+        <v>448814</v>
       </c>
       <c r="R22" t="n">
-        <v>7094549</v>
+        <v>7094591</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2891,7 +2790,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2918,15 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117894257</v>
+        <v>117894267</v>
       </c>
       <c r="B23" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2958,10 +2852,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>448356</v>
+        <v>448851</v>
       </c>
       <c r="R23" t="n">
-        <v>7094667</v>
+        <v>7094596</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3025,15 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117894264</v>
+        <v>117894268</v>
       </c>
       <c r="B24" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3065,10 +2954,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>448772</v>
+        <v>448849</v>
       </c>
       <c r="R24" t="n">
-        <v>7094608</v>
+        <v>7094603</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3132,15 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117894252</v>
+        <v>117894269</v>
       </c>
       <c r="B25" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3172,10 +3056,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>448177</v>
+        <v>448847</v>
       </c>
       <c r="R25" t="n">
-        <v>7094570</v>
+        <v>7094604</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3212,7 +3096,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3239,15 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117894249</v>
+        <v>117894270</v>
       </c>
       <c r="B26" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3279,10 +3158,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>448332</v>
+        <v>448883</v>
       </c>
       <c r="R26" t="n">
-        <v>7094545</v>
+        <v>7094577</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3346,15 +3225,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117894255</v>
+        <v>117894271</v>
       </c>
       <c r="B27" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3362,16 +3236,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3379,17 +3253,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Rörvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>448322</v>
+        <v>448815</v>
       </c>
       <c r="R27" t="n">
-        <v>7094686</v>
+        <v>7094592</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3424,11 +3314,6 @@
           <t>2024-06-19</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3450,429 +3335,6 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>117894276</v>
-      </c>
-      <c r="B28" t="n">
-        <v>90521</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Rörvattnet V, Jmt</t>
-        </is>
-      </c>
-      <c r="Q28" t="n">
-        <v>448261</v>
-      </c>
-      <c r="R28" t="n">
-        <v>7094615</v>
-      </c>
-      <c r="S28" t="n">
-        <v>10</v>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>Hotagen</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AD28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="inlineStr"/>
-      <c r="AW28" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>117894251</v>
-      </c>
-      <c r="B29" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Rörvattnet V, Jmt</t>
-        </is>
-      </c>
-      <c r="Q29" t="n">
-        <v>448162</v>
-      </c>
-      <c r="R29" t="n">
-        <v>7094481</v>
-      </c>
-      <c r="S29" t="n">
-        <v>10</v>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>Hotagen</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="inlineStr"/>
-      <c r="AW29" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>117894256</v>
-      </c>
-      <c r="B30" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Rörvattnet V, Jmt</t>
-        </is>
-      </c>
-      <c r="Q30" t="n">
-        <v>448339</v>
-      </c>
-      <c r="R30" t="n">
-        <v>7094675</v>
-      </c>
-      <c r="S30" t="n">
-        <v>10</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Hotagen</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
-        </is>
-      </c>
-      <c r="AD30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>117894262</v>
-      </c>
-      <c r="B31" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Rörvattnet V, Jmt</t>
-        </is>
-      </c>
-      <c r="Q31" t="n">
-        <v>448775</v>
-      </c>
-      <c r="R31" t="n">
-        <v>7094632</v>
-      </c>
-      <c r="S31" t="n">
-        <v>10</v>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>Hotagen</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="inlineStr"/>
-      <c r="AW31" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23439-2024 artfynd.xlsx
+++ b/artfynd/A 23439-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117894245</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117894246</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117894247</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117894248</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117894249</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117894250</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117894251</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117894252</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1590,6 +1635,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117894253</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1692,6 +1742,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117894254</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1794,6 +1849,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117894255</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1896,6 +1956,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117894256</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1998,6 +2063,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117894257</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2100,6 +2170,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117894258</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2202,6 +2277,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117894259</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2304,6 +2384,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117894260</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2406,6 +2491,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117894262</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2508,6 +2598,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117894263</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2610,6 +2705,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117894264</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2712,6 +2812,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117894265</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2814,6 +2919,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117894266</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2916,6 +3026,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117894267</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3018,6 +3133,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117894268</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3120,6 +3240,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117894269</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3222,6 +3347,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117894270</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3335,8 +3465,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117894271</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>